--- a/artfynd/A 30704-2021 artfynd.xlsx
+++ b/artfynd/A 30704-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190679</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30704-2021 artfynd.xlsx
+++ b/artfynd/A 30704-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190679</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30704-2021 artfynd.xlsx
+++ b/artfynd/A 30704-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190679</v>
       </c>
       <c r="B2" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30704-2021 artfynd.xlsx
+++ b/artfynd/A 30704-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190679</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30704-2021 artfynd.xlsx
+++ b/artfynd/A 30704-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130190679</v>
+        <v>406015</v>
       </c>
       <c r="B2" t="n">
-        <v>80316</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skellefteå-Umeå, Vb</t>
+          <t>Öster om Röjmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763430</v>
+        <v>763317</v>
       </c>
       <c r="R2" t="n">
-        <v>7186572</v>
+        <v>7186397</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>06:49</t>
+          <t>2008-10-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>06:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>2008-10-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,18 +757,140 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130190679</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skellefteå-Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>763430</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7186572</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jonas Mattsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Magnus Lundin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
